--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8522,0.0120,0.0099,0.1124</t>
-  </si>
-  <si>
-    <t>0.0015,0.0008,0.0007,0.9989</t>
-  </si>
-  <si>
-    <t>0.4030,0.0085,0.0004,0.7097</t>
-  </si>
-  <si>
-    <t>0.0287,0.0062,0.0023,0.9858</t>
-  </si>
-  <si>
-    <t>0.9973,0.0012,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9952,0.0041,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9863,0.0080,0.0040,0.0009</t>
-  </si>
-  <si>
-    <t>0.9975,0.0008,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9897,0.0113,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9949,0.0035,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9960,0.0013,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9967,0.0006,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.8874,0.0251,0.0778,0.0019</t>
-  </si>
-  <si>
-    <t>0.3675,0.0623,0.6914,0.0021</t>
-  </si>
-  <si>
-    <t>0.0688,0.1335,0.8644,0.0008</t>
-  </si>
-  <si>
-    <t>0.0723,0.0471,0.8703,0.0015</t>
-  </si>
-  <si>
-    <t>0.6591,0.0397,0.4074,0.0115</t>
-  </si>
-  <si>
-    <t>0.0723,0.9443,0.0086,0.0015</t>
-  </si>
-  <si>
-    <t>0.0431,0.9630,0.0072,0.0008</t>
-  </si>
-  <si>
-    <t>0.2745,0.8331,0.0036,0.0012</t>
-  </si>
-  <si>
-    <t>0.0660,0.9351,0.0107,0.0055</t>
-  </si>
-  <si>
-    <t>0.0079,0.9889,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.5610,0.0178,0.5105,0.0129</t>
-  </si>
-  <si>
-    <t>0.4038,0.0520,0.5592,0.0356</t>
-  </si>
-  <si>
-    <t>0.0316,0.0114,0.9627,0.0012</t>
-  </si>
-  <si>
-    <t>0.0679,0.0289,0.9135,0.0095</t>
-  </si>
-  <si>
-    <t>0.1464,0.0098,0.9113,0.0009</t>
-  </si>
-  <si>
-    <t>0.1212,0.0088,0.8950,0.0066</t>
-  </si>
-  <si>
-    <t>0.0021,0.0026,0.9957,0.0004</t>
-  </si>
-  <si>
-    <t>0.7594,0.2672,0.0295,0.0022</t>
-  </si>
-  <si>
-    <t>0.2651,0.4908,0.2845,0.0056</t>
-  </si>
-  <si>
-    <t>0.0023,0.0139,0.9905,0.0038</t>
-  </si>
-  <si>
-    <t>0.0018,0.9753,0.0708,0.0001</t>
-  </si>
-  <si>
-    <t>0.8513,0.1241,0.0279,0.0103</t>
-  </si>
-  <si>
-    <t>0.6438,0.1706,0.1705,0.0030</t>
-  </si>
-  <si>
-    <t>0.6240,0.5012,0.0118,0.0007</t>
-  </si>
-  <si>
-    <t>0.1098,0.8063,0.3826,0.0113</t>
-  </si>
-  <si>
-    <t>0.0039,0.7627,0.9174,0.0009</t>
-  </si>
-  <si>
-    <t>0.0170,0.0545,0.9596,0.0123</t>
-  </si>
-  <si>
-    <t>0.1104,0.0090,0.8447,0.0417</t>
-  </si>
-  <si>
-    <t>0.1031,0.0027,0.6479,0.2097</t>
-  </si>
-  <si>
-    <t>0.0303,0.2650,0.9121,0.0037</t>
-  </si>
-  <si>
-    <t>0.0032,0.9669,0.0278,0.0003</t>
-  </si>
-  <si>
-    <t>0.0117,0.0184,0.9635,0.0095</t>
-  </si>
-  <si>
-    <t>0.2789,0.5081,0.3299,0.1912</t>
-  </si>
-  <si>
-    <t>0.0225,0.9496,0.0152,0.0100</t>
-  </si>
-  <si>
-    <t>0.0021,0.9878,0.0430,0.0010</t>
-  </si>
-  <si>
-    <t>0.0138,0.9575,0.1534,0.0037</t>
-  </si>
-  <si>
-    <t>0.0117,0.1784,0.9072,0.0171</t>
-  </si>
-  <si>
-    <t>0.0011,0.2179,0.9848,0.0008</t>
-  </si>
-  <si>
-    <t>0.0098,0.0015,0.9660,0.0430</t>
-  </si>
-  <si>
-    <t>0.0074,0.0014,0.9906,0.0009</t>
-  </si>
-  <si>
-    <t>0.0011,0.0056,0.9912,0.0073</t>
-  </si>
-  <si>
-    <t>0.1026,0.0589,0.8879,0.0051</t>
-  </si>
-  <si>
-    <t>0.8547,0.1991,0.0076,0.0030</t>
-  </si>
-  <si>
-    <t>0.9731,0.0068,0.0152,0.0034</t>
-  </si>
-  <si>
-    <t>0.9709,0.0171,0.0068,0.0026</t>
-  </si>
-  <si>
-    <t>0.0016,0.0115,0.9930,0.0029</t>
-  </si>
-  <si>
-    <t>0.9888,0.0059,0.0017,0.0012</t>
-  </si>
-  <si>
-    <t>0.9827,0.0187,0.0013,0.0009</t>
-  </si>
-  <si>
-    <t>0.9359,0.0979,0.0053,0.0011</t>
-  </si>
-  <si>
-    <t>0.0004,0.7618,0.9917,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.0202,0.9866,0.0043</t>
-  </si>
-  <si>
-    <t>0.0031,0.0029,0.9894,0.0049</t>
-  </si>
-  <si>
-    <t>0.0003,0.9478,0.9723,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0068,0.9946,0.0034</t>
-  </si>
-  <si>
-    <t>0.0409,0.9043,0.1253,0.0015</t>
-  </si>
-  <si>
-    <t>0.0041,0.9882,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.2549,0.0586,0.8093,0.0122</t>
-  </si>
-  <si>
-    <t>0.4203,0.5992,0.0440,0.0083</t>
-  </si>
-  <si>
-    <t>0.0743,0.1066,0.8402,0.0053</t>
-  </si>
-  <si>
-    <t>0.0011,0.7101,0.9767,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.8740,0.8815,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9840,0.7010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.9249,0.7699,0.0002</t>
-  </si>
-  <si>
-    <t>0.0166,0.0014,0.0182,0.9818</t>
-  </si>
-  <si>
-    <t>0.0028,0.0066,0.0005,0.9976</t>
-  </si>
-  <si>
-    <t>0.0138,0.0121,0.0038,0.9900</t>
-  </si>
-  <si>
-    <t>0.0279,0.0009,0.0049,0.9833</t>
-  </si>
-  <si>
-    <t>0.0072,0.0055,0.0023,0.9947</t>
-  </si>
-  <si>
-    <t>0.0082,0.0092,0.0025,0.9930</t>
-  </si>
-  <si>
-    <t>0.0004,0.9749,0.8829,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.8276,0.9486,0.0001</t>
-  </si>
-  <si>
-    <t>0.0145,0.5645,0.8694,0.0025</t>
-  </si>
-  <si>
-    <t>0.0006,0.9436,0.9279,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.9566,0.9101,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.9112,0.7966,0.0006</t>
-  </si>
-  <si>
-    <t>0.9942,0.0041,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9469,0.1033,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9776,0.0293,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.9947,0.0029,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9805,0.0209,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.9980,0.0009,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9866,0.0123,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.9868,0.0177,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9973,0.0005,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9946,0.0036,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9979,0.0004,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9976,0.0014,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9955,0.0014,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9975,0.0010,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9941,0.0016,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9925,0.0049,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.1186,0.0061,0.8635,0.0298</t>
-  </si>
-  <si>
-    <t>0.0616,0.0113,0.9568,0.0010</t>
-  </si>
-  <si>
-    <t>0.6856,0.0126,0.2277,0.0590</t>
-  </si>
-  <si>
-    <t>0.1976,0.0086,0.8208,0.0186</t>
-  </si>
-  <si>
-    <t>0.0090,0.9851,0.0045,0.0003</t>
-  </si>
-  <si>
-    <t>0.0394,0.9467,0.0307,0.0004</t>
-  </si>
-  <si>
-    <t>0.1539,0.8701,0.0130,0.0029</t>
-  </si>
-  <si>
-    <t>0.1901,0.8255,0.0148,0.0027</t>
-  </si>
-  <si>
-    <t>0.0206,0.9764,0.0094,0.0003</t>
-  </si>
-  <si>
-    <t>0.0052,0.9889,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.4249,0.6759,0.0088,0.0036</t>
-  </si>
-  <si>
-    <t>0.5499,0.1383,0.4232,0.0408</t>
-  </si>
-  <si>
-    <t>0.0489,0.0109,0.9496,0.0043</t>
-  </si>
-  <si>
-    <t>0.1773,0.5630,0.2980,0.0207</t>
-  </si>
-  <si>
-    <t>0.6437,0.0195,0.4258,0.0124</t>
-  </si>
-  <si>
-    <t>0.0631,0.1200,0.0177,0.9412</t>
-  </si>
-  <si>
-    <t>0.0072,0.9774,0.0347,0.0024</t>
-  </si>
-  <si>
-    <t>0.0236,0.9432,0.0417,0.0099</t>
-  </si>
-  <si>
-    <t>0.0056,0.9447,0.0460,0.0901</t>
-  </si>
-  <si>
-    <t>0.0009,0.9050,0.9297,0.0002</t>
-  </si>
-  <si>
-    <t>0.0111,0.9791,0.0444,0.0004</t>
-  </si>
-  <si>
-    <t>0.7314,0.4122,0.0075,0.0006</t>
-  </si>
-  <si>
-    <t>0.2234,0.7779,0.0749,0.0024</t>
-  </si>
-  <si>
-    <t>0.9554,0.0474,0.0042,0.0020</t>
-  </si>
-  <si>
-    <t>0.9919,0.0016,0.0001,0.0027</t>
-  </si>
-  <si>
-    <t>0.9906,0.0020,0.0007,0.0025</t>
-  </si>
-  <si>
-    <t>0.9718,0.0093,0.0078,0.0066</t>
-  </si>
-  <si>
-    <t>0.9843,0.0033,0.0017,0.0043</t>
-  </si>
-  <si>
-    <t>0.9390,0.0429,0.0135,0.0075</t>
-  </si>
-  <si>
-    <t>0.9928,0.0020,0.0006,0.0015</t>
-  </si>
-  <si>
-    <t>0.9899,0.0057,0.0028,0.0005</t>
-  </si>
-  <si>
-    <t>0.0044,0.7317,0.9271,0.0010</t>
-  </si>
-  <si>
-    <t>0.0027,0.7362,0.9553,0.0002</t>
-  </si>
-  <si>
-    <t>0.0024,0.0359,0.9895,0.0008</t>
-  </si>
-  <si>
-    <t>0.0715,0.0153,0.9534,0.0002</t>
-  </si>
-  <si>
-    <t>0.9014,0.0079,0.0501,0.0097</t>
-  </si>
-  <si>
-    <t>0.5417,0.0378,0.5552,0.0012</t>
-  </si>
-  <si>
-    <t>0.4991,0.0063,0.5798,0.0157</t>
-  </si>
-  <si>
-    <t>0.5249,0.2462,0.2613,0.0102</t>
-  </si>
-  <si>
-    <t>0.1882,0.0007,0.0009,0.9360</t>
-  </si>
-  <si>
-    <t>0.0002,0.0069,0.0024,0.9984</t>
-  </si>
-  <si>
-    <t>0.0060,0.0078,0.0010,0.9955</t>
-  </si>
-  <si>
-    <t>0.0394,0.0003,0.0016,0.9877</t>
-  </si>
-  <si>
-    <t>0.0013,0.8307,0.9440,0.0004</t>
-  </si>
-  <si>
-    <t>0.9629,0.0307,0.0044,0.0040</t>
-  </si>
-  <si>
-    <t>0.4087,0.6064,0.0304,0.0023</t>
-  </si>
-  <si>
-    <t>0.9872,0.0059,0.0012,0.0016</t>
-  </si>
-  <si>
-    <t>0.7193,0.4133,0.0065,0.0010</t>
-  </si>
-  <si>
-    <t>0.9848,0.0033,0.0023,0.0029</t>
-  </si>
-  <si>
-    <t>0.7606,0.0040,0.0072,0.2859</t>
-  </si>
-  <si>
-    <t>0.9883,0.0024,0.0009,0.0026</t>
-  </si>
-  <si>
-    <t>0.0004,0.0213,0.9862,0.0239</t>
-  </si>
-  <si>
-    <t>0.9460,0.0002,0.0011,0.0566</t>
-  </si>
-  <si>
-    <t>0.9078,0.0091,0.0277,0.0440</t>
-  </si>
-  <si>
-    <t>0.1167,0.8399,0.0419,0.0292</t>
-  </si>
-  <si>
-    <t>0.9307,0.0651,0.0039,0.0028</t>
-  </si>
-  <si>
-    <t>0.8199,0.1635,0.0375,0.0059</t>
-  </si>
-  <si>
-    <t>0.1056,0.7870,0.1673,0.0171</t>
-  </si>
-  <si>
-    <t>0.8131,0.0381,0.2434,0.0036</t>
-  </si>
-  <si>
-    <t>0.8934,0.0518,0.0368,0.0050</t>
-  </si>
-  <si>
-    <t>0.9961,0.0010,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9783,0.0196,0.0006,0.0021</t>
-  </si>
-  <si>
-    <t>0.9881,0.0036,0.0047,0.0011</t>
-  </si>
-  <si>
-    <t>0.9908,0.0011,0.0014,0.0026</t>
-  </si>
-  <si>
-    <t>0.9780,0.0107,0.0048,0.0026</t>
-  </si>
-  <si>
-    <t>0.9913,0.0046,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9921,0.0012,0.0007,0.0022</t>
-  </si>
-  <si>
-    <t>0.9878,0.0006,0.0002,0.0101</t>
-  </si>
-  <si>
-    <t>0.7380,0.3336,0.0104,0.0091</t>
-  </si>
-  <si>
-    <t>0.5255,0.6779,0.0020,0.0004</t>
-  </si>
-  <si>
-    <t>0.8061,0.2846,0.0077,0.0010</t>
-  </si>
-  <si>
-    <t>0.0666,0.6936,0.5896,0.0013</t>
-  </si>
-  <si>
-    <t>0.9457,0.0502,0.0004,0.0032</t>
-  </si>
-  <si>
-    <t>0.7827,0.1243,0.1582,0.0117</t>
-  </si>
-  <si>
-    <t>0.9465,0.0638,0.0065,0.0013</t>
-  </si>
-  <si>
-    <t>0.4376,0.5737,0.0385,0.0039</t>
-  </si>
-  <si>
-    <t>0.0003,0.0222,0.9983,0.0003</t>
-  </si>
-  <si>
-    <t>0.9411,0.0610,0.0058,0.0042</t>
-  </si>
-  <si>
-    <t>0.0030,0.0272,0.9914,0.0002</t>
-  </si>
-  <si>
-    <t>0.0075,0.1124,0.9770,0.0006</t>
-  </si>
-  <si>
-    <t>0.0102,0.0064,0.9862,0.0015</t>
-  </si>
-  <si>
-    <t>0.0022,0.2261,0.9691,0.0017</t>
-  </si>
-  <si>
-    <t>0.0824,0.0042,0.9540,0.0007</t>
-  </si>
-  <si>
-    <t>0.1303,0.0024,0.9433,0.0004</t>
-  </si>
-  <si>
-    <t>0.0034,0.0307,0.9906,0.0002</t>
-  </si>
-  <si>
-    <t>0.0903,0.0699,0.8763,0.0108</t>
-  </si>
-  <si>
-    <t>0.1173,0.0302,0.8856,0.0017</t>
-  </si>
-  <si>
-    <t>0.2222,0.0710,0.7567,0.0028</t>
-  </si>
-  <si>
-    <t>0.1527,0.1279,0.7113,0.0017</t>
-  </si>
-  <si>
-    <t>0.1494,0.4669,0.5737,0.0088</t>
-  </si>
-  <si>
-    <t>0.5206,0.2719,0.1844,0.0136</t>
-  </si>
-  <si>
-    <t>0.6724,0.1427,0.1888,0.0393</t>
-  </si>
-  <si>
-    <t>0.1756,0.0976,0.7852,0.0025</t>
-  </si>
-  <si>
-    <t>0.7510,0.3650,0.0097,0.0005</t>
-  </si>
-  <si>
-    <t>0.2821,0.8352,0.0021,0.0006</t>
-  </si>
-  <si>
-    <t>0.8745,0.1762,0.0038,0.0029</t>
-  </si>
-  <si>
-    <t>0.9732,0.0320,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.9425,0.0959,0.0018,0.0008</t>
-  </si>
-  <si>
-    <t>0.6455,0.0385,0.3500,0.0262</t>
-  </si>
-  <si>
-    <t>0.6685,0.0075,0.5194,0.0039</t>
-  </si>
-  <si>
-    <t>0.7437,0.0136,0.1519,0.0697</t>
-  </si>
-  <si>
-    <t>0.4798,0.0243,0.5772,0.0172</t>
-  </si>
-  <si>
-    <t>0.8829,0.0070,0.1058,0.0068</t>
-  </si>
-  <si>
-    <t>0.0121,0.0253,0.9406,0.0447</t>
-  </si>
-  <si>
-    <t>0.0133,0.6085,0.8860,0.0096</t>
-  </si>
-  <si>
-    <t>0.0603,0.1763,0.8914,0.0019</t>
-  </si>
-  <si>
-    <t>0.0305,0.4553,0.6624,0.0007</t>
-  </si>
-  <si>
-    <t>0.0049,0.5776,0.9073,0.0013</t>
-  </si>
-  <si>
-    <t>0.9772,0.0252,0.0013,0.0013</t>
-  </si>
-  <si>
-    <t>0.9799,0.0136,0.0038,0.0016</t>
-  </si>
-  <si>
-    <t>0.9829,0.0151,0.0008,0.0015</t>
-  </si>
-  <si>
-    <t>0.9940,0.0041,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9949,0.0041,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9819,0.0261,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9900,0.0036,0.0007,0.0020</t>
-  </si>
-  <si>
-    <t>0.9919,0.0055,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.2043,0.0799,0.8107,0.0093</t>
-  </si>
-  <si>
-    <t>0.3854,0.4526,0.2947,0.0286</t>
-  </si>
-  <si>
-    <t>0.7160,0.0851,0.2005,0.0234</t>
-  </si>
-  <si>
-    <t>0.0040,0.0626,0.9878,0.0005</t>
-  </si>
-  <si>
-    <t>0.0027,0.0212,0.9853,0.0034</t>
-  </si>
-  <si>
-    <t>0.0135,0.2224,0.8893,0.0021</t>
-  </si>
-  <si>
-    <t>0.0029,0.0047,0.9917,0.0014</t>
-  </si>
-  <si>
-    <t>0.1211,0.0613,0.8051,0.0040</t>
-  </si>
-  <si>
-    <t>0.0029,0.0072,0.9934,0.0005</t>
-  </si>
-  <si>
-    <t>0.0077,0.0070,0.9739,0.0215</t>
-  </si>
-  <si>
-    <t>0.0312,0.0620,0.9388,0.0169</t>
-  </si>
-  <si>
-    <t>0.7976,0.0097,0.1510,0.0307</t>
-  </si>
-  <si>
-    <t>0.3713,0.0054,0.6888,0.0166</t>
-  </si>
-  <si>
-    <t>0.6075,0.0119,0.3596,0.0448</t>
-  </si>
-  <si>
-    <t>0.9952,0.0034,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9771,0.0307,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.9950,0.0038,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9792,0.0254,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.9935,0.0025,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9883,0.0131,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9735,0.0481,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9889,0.0040,0.0004,0.0026</t>
-  </si>
-  <si>
-    <t>0.0210,0.0602,0.9473,0.0003</t>
-  </si>
-  <si>
-    <t>0.0114,0.0363,0.9800,0.0008</t>
-  </si>
-  <si>
-    <t>0.0035,0.0862,0.9759,0.0008</t>
-  </si>
-  <si>
-    <t>0.2555,0.0143,0.8353,0.0008</t>
-  </si>
-  <si>
-    <t>0.0037,0.0162,0.9855,0.0052</t>
-  </si>
-  <si>
-    <t>0.2357,0.0023,0.7780,0.0256</t>
-  </si>
-  <si>
-    <t>0.1460,0.0077,0.9083,0.0019</t>
-  </si>
-  <si>
-    <t>0.0635,0.0645,0.8323,0.0912</t>
-  </si>
-  <si>
-    <t>0.5187,0.0017,0.0313,0.4395</t>
-  </si>
-  <si>
-    <t>0.1227,0.0330,0.0061,0.9356</t>
-  </si>
-  <si>
-    <t>0.4072,0.0009,0.0023,0.7696</t>
-  </si>
-  <si>
-    <t>0.0049,0.0006,0.0012,0.9972</t>
-  </si>
-  <si>
-    <t>0.0037,0.0039,0.0017,0.9966</t>
-  </si>
-  <si>
-    <t>0.9327,0.0033,0.0232,0.0179</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9018,0.0200,0.0209,0.0283</t>
+  </si>
+  <si>
+    <t>0.0632,0.0012,0.0027,0.9707</t>
+  </si>
+  <si>
+    <t>0.8234,0.0031,0.0030,0.2464</t>
+  </si>
+  <si>
+    <t>0.3980,0.0046,0.0140,0.7158</t>
+  </si>
+  <si>
+    <t>0.9955,0.0029,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0004,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9909,0.0052,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.9973,0.0008,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9911,0.0044,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.9891,0.0160,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0012,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0011,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.6747,0.1466,0.1481,0.0267</t>
+  </si>
+  <si>
+    <t>0.2737,0.0550,0.7652,0.0068</t>
+  </si>
+  <si>
+    <t>0.6354,0.0537,0.4260,0.0113</t>
+  </si>
+  <si>
+    <t>0.3970,0.0483,0.5938,0.0018</t>
+  </si>
+  <si>
+    <t>0.5281,0.0470,0.5628,0.0045</t>
+  </si>
+  <si>
+    <t>0.0206,0.9776,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.0096,0.9834,0.0159,0.0006</t>
+  </si>
+  <si>
+    <t>0.3123,0.7641,0.0187,0.0052</t>
+  </si>
+  <si>
+    <t>0.0561,0.9490,0.0096,0.0008</t>
+  </si>
+  <si>
+    <t>0.0122,0.9849,0.0038,0.0009</t>
+  </si>
+  <si>
+    <t>0.6895,0.0170,0.3560,0.0166</t>
+  </si>
+  <si>
+    <t>0.5813,0.0097,0.5279,0.0053</t>
+  </si>
+  <si>
+    <t>0.0247,0.0100,0.9668,0.0012</t>
+  </si>
+  <si>
+    <t>0.2244,0.0087,0.7433,0.0445</t>
+  </si>
+  <si>
+    <t>0.1054,0.0236,0.8989,0.0020</t>
+  </si>
+  <si>
+    <t>0.0412,0.0118,0.9489,0.0060</t>
+  </si>
+  <si>
+    <t>0.0004,0.0016,0.9918,0.0220</t>
+  </si>
+  <si>
+    <t>0.4483,0.5664,0.0374,0.0119</t>
+  </si>
+  <si>
+    <t>0.5366,0.2533,0.2334,0.0034</t>
+  </si>
+  <si>
+    <t>0.0005,0.0045,0.9956,0.0033</t>
+  </si>
+  <si>
+    <t>0.0063,0.7942,0.6529,0.0001</t>
+  </si>
+  <si>
+    <t>0.9262,0.0106,0.0010,0.0462</t>
+  </si>
+  <si>
+    <t>0.2433,0.0379,0.7683,0.0060</t>
+  </si>
+  <si>
+    <t>0.6497,0.4819,0.0073,0.0019</t>
+  </si>
+  <si>
+    <t>0.0265,0.9414,0.0939,0.0057</t>
+  </si>
+  <si>
+    <t>0.0588,0.2398,0.8000,0.0148</t>
+  </si>
+  <si>
+    <t>0.2979,0.0409,0.7098,0.0333</t>
+  </si>
+  <si>
+    <t>0.0397,0.0400,0.8667,0.1365</t>
+  </si>
+  <si>
+    <t>0.0901,0.0036,0.7358,0.1451</t>
+  </si>
+  <si>
+    <t>0.0259,0.1854,0.9242,0.0012</t>
+  </si>
+  <si>
+    <t>0.0015,0.9814,0.0073,0.0007</t>
+  </si>
+  <si>
+    <t>0.0093,0.0166,0.9681,0.0190</t>
+  </si>
+  <si>
+    <t>0.0018,0.8265,0.0030,0.8542</t>
+  </si>
+  <si>
+    <t>0.0121,0.9602,0.0206,0.0260</t>
+  </si>
+  <si>
+    <t>0.0059,0.9751,0.0723,0.0011</t>
+  </si>
+  <si>
+    <t>0.0101,0.9622,0.0731,0.0059</t>
+  </si>
+  <si>
+    <t>0.0015,0.1791,0.9280,0.0254</t>
+  </si>
+  <si>
+    <t>0.0109,0.3083,0.9170,0.0010</t>
+  </si>
+  <si>
+    <t>0.0274,0.0013,0.9475,0.0401</t>
+  </si>
+  <si>
+    <t>0.0431,0.0018,0.9786,0.0002</t>
+  </si>
+  <si>
+    <t>0.0074,0.0114,0.9919,0.0001</t>
+  </si>
+  <si>
+    <t>0.0075,0.1020,0.9753,0.0013</t>
+  </si>
+  <si>
+    <t>0.7541,0.4034,0.0027,0.0011</t>
+  </si>
+  <si>
+    <t>0.9910,0.0061,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9947,0.0015,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.0029,0.0430,0.9865,0.0045</t>
+  </si>
+  <si>
+    <t>0.9946,0.0026,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9738,0.0254,0.0052,0.0008</t>
+  </si>
+  <si>
+    <t>0.9887,0.0130,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9118,0.9898,0.0000</t>
+  </si>
+  <si>
+    <t>0.0099,0.0477,0.9489,0.0235</t>
+  </si>
+  <si>
+    <t>0.0012,0.0042,0.9839,0.0378</t>
+  </si>
+  <si>
+    <t>0.0004,0.9534,0.9399,0.0002</t>
+  </si>
+  <si>
+    <t>0.0037,0.0048,0.9954,0.0004</t>
+  </si>
+  <si>
+    <t>0.0219,0.9155,0.0536,0.0005</t>
+  </si>
+  <si>
+    <t>0.0032,0.9913,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.3708,0.0226,0.6880,0.0276</t>
+  </si>
+  <si>
+    <t>0.5052,0.4668,0.1451,0.0217</t>
+  </si>
+  <si>
+    <t>0.0135,0.0568,0.9498,0.0053</t>
+  </si>
+  <si>
+    <t>0.0008,0.9461,0.8615,0.0002</t>
+  </si>
+  <si>
+    <t>0.0032,0.6861,0.9595,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.9815,0.4829,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9635,0.9047,0.0000</t>
+  </si>
+  <si>
+    <t>0.0280,0.0019,0.1318,0.9164</t>
+  </si>
+  <si>
+    <t>0.0085,0.0051,0.0005,0.9958</t>
+  </si>
+  <si>
+    <t>0.0036,0.0155,0.0003,0.9967</t>
+  </si>
+  <si>
+    <t>0.0048,0.0027,0.0009,0.9971</t>
+  </si>
+  <si>
+    <t>0.0135,0.0051,0.0057,0.9908</t>
+  </si>
+  <si>
+    <t>0.0056,0.0183,0.0003,0.9959</t>
+  </si>
+  <si>
+    <t>0.0012,0.9207,0.9212,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.8933,0.9487,0.0002</t>
+  </si>
+  <si>
+    <t>0.0040,0.3571,0.9574,0.0001</t>
+  </si>
+  <si>
+    <t>0.0258,0.3501,0.9331,0.0041</t>
+  </si>
+  <si>
+    <t>0.0002,0.9533,0.9355,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.8824,0.9716,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0039,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9860,0.0197,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9594,0.0835,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.9911,0.0061,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9948,0.0025,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9967,0.0013,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9863,0.0158,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9893,0.0076,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.9968,0.0008,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9932,0.0053,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9886,0.0099,0.0034,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0018,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9963,0.0024,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9931,0.0032,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.0083,0.0043,0.9885,0.0034</t>
+  </si>
+  <si>
+    <t>0.2940,0.0037,0.8394,0.0022</t>
+  </si>
+  <si>
+    <t>0.7319,0.0111,0.2292,0.0297</t>
+  </si>
+  <si>
+    <t>0.0087,0.0062,0.9818,0.0042</t>
+  </si>
+  <si>
+    <t>0.0102,0.9858,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.0171,0.9795,0.0078,0.0002</t>
+  </si>
+  <si>
+    <t>0.0703,0.9351,0.0059,0.0017</t>
+  </si>
+  <si>
+    <t>0.2357,0.8139,0.0045,0.0044</t>
+  </si>
+  <si>
+    <t>0.0174,0.9708,0.0191,0.0010</t>
+  </si>
+  <si>
+    <t>0.0023,0.9955,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.2698,0.8052,0.0058,0.0003</t>
+  </si>
+  <si>
+    <t>0.5321,0.3527,0.0773,0.0208</t>
+  </si>
+  <si>
+    <t>0.6282,0.0178,0.4571,0.0093</t>
+  </si>
+  <si>
+    <t>0.5473,0.1480,0.3290,0.0155</t>
+  </si>
+  <si>
+    <t>0.5660,0.0273,0.5354,0.0059</t>
+  </si>
+  <si>
+    <t>0.0244,0.0778,0.0264,0.9679</t>
+  </si>
+  <si>
+    <t>0.0088,0.9766,0.0637,0.0015</t>
+  </si>
+  <si>
+    <t>0.0028,0.9852,0.0110,0.0052</t>
+  </si>
+  <si>
+    <t>0.0457,0.8269,0.0743,0.2140</t>
+  </si>
+  <si>
+    <t>0.0007,0.8232,0.9585,0.0004</t>
+  </si>
+  <si>
+    <t>0.0147,0.9801,0.0187,0.0003</t>
+  </si>
+  <si>
+    <t>0.7341,0.2647,0.0616,0.0026</t>
+  </si>
+  <si>
+    <t>0.7078,0.3383,0.0280,0.0012</t>
+  </si>
+  <si>
+    <t>0.9458,0.0311,0.0248,0.0023</t>
+  </si>
+  <si>
+    <t>0.9927,0.0028,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9951,0.0007,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9760,0.0124,0.0040,0.0032</t>
+  </si>
+  <si>
+    <t>0.9952,0.0011,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9636,0.0091,0.0180,0.0075</t>
+  </si>
+  <si>
+    <t>0.9882,0.0025,0.0015,0.0036</t>
+  </si>
+  <si>
+    <t>0.9861,0.0046,0.0033,0.0017</t>
+  </si>
+  <si>
+    <t>0.0007,0.9063,0.9460,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.4565,0.9815,0.0002</t>
+  </si>
+  <si>
+    <t>0.0067,0.1224,0.9809,0.0001</t>
+  </si>
+  <si>
+    <t>0.0599,0.0317,0.9300,0.0014</t>
+  </si>
+  <si>
+    <t>0.8448,0.0093,0.0506,0.0463</t>
+  </si>
+  <si>
+    <t>0.7009,0.0410,0.2364,0.0602</t>
+  </si>
+  <si>
+    <t>0.1785,0.0035,0.8498,0.0210</t>
+  </si>
+  <si>
+    <t>0.6990,0.0984,0.2499,0.0256</t>
+  </si>
+  <si>
+    <t>0.3993,0.0039,0.0009,0.8010</t>
+  </si>
+  <si>
+    <t>0.0004,0.0018,0.0026,0.9987</t>
+  </si>
+  <si>
+    <t>0.0022,0.0010,0.0006,0.9983</t>
+  </si>
+  <si>
+    <t>0.0242,0.0018,0.0016,0.9891</t>
+  </si>
+  <si>
+    <t>0.0013,0.8817,0.8712,0.0002</t>
+  </si>
+  <si>
+    <t>0.9704,0.0128,0.0027,0.0058</t>
+  </si>
+  <si>
+    <t>0.3688,0.6378,0.0655,0.0156</t>
+  </si>
+  <si>
+    <t>0.9769,0.0117,0.0006,0.0049</t>
+  </si>
+  <si>
+    <t>0.7717,0.3511,0.0051,0.0009</t>
+  </si>
+  <si>
+    <t>0.9920,0.0011,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.2699,0.0230,0.0621,0.7380</t>
+  </si>
+  <si>
+    <t>0.9695,0.0146,0.0059,0.0036</t>
+  </si>
+  <si>
+    <t>0.0032,0.0112,0.9835,0.0238</t>
+  </si>
+  <si>
+    <t>0.7674,0.0003,0.0028,0.3301</t>
+  </si>
+  <si>
+    <t>0.9489,0.0036,0.0182,0.0157</t>
+  </si>
+  <si>
+    <t>0.1892,0.8211,0.0080,0.0079</t>
+  </si>
+  <si>
+    <t>0.8291,0.1587,0.0081,0.0127</t>
+  </si>
+  <si>
+    <t>0.8326,0.1704,0.0332,0.0028</t>
+  </si>
+  <si>
+    <t>0.2722,0.7033,0.0539,0.0085</t>
+  </si>
+  <si>
+    <t>0.8129,0.0614,0.1090,0.0195</t>
+  </si>
+  <si>
+    <t>0.7285,0.2608,0.0404,0.0122</t>
+  </si>
+  <si>
+    <t>0.9933,0.0003,0.0004,0.0030</t>
+  </si>
+  <si>
+    <t>0.9929,0.0022,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9919,0.0034,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9875,0.0027,0.0026,0.0022</t>
+  </si>
+  <si>
+    <t>0.9836,0.0069,0.0038,0.0017</t>
+  </si>
+  <si>
+    <t>0.9950,0.0010,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9910,0.0045,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9958,0.0006,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.7197,0.3740,0.0067,0.0059</t>
+  </si>
+  <si>
+    <t>0.6021,0.5440,0.0079,0.0010</t>
+  </si>
+  <si>
+    <t>0.5867,0.5177,0.0140,0.0013</t>
+  </si>
+  <si>
+    <t>0.7760,0.2518,0.0263,0.0113</t>
+  </si>
+  <si>
+    <t>0.9649,0.0548,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9693,0.0252,0.0034,0.0020</t>
+  </si>
+  <si>
+    <t>0.9527,0.0446,0.0075,0.0023</t>
+  </si>
+  <si>
+    <t>0.8836,0.1351,0.0124,0.0078</t>
+  </si>
+  <si>
+    <t>0.0014,0.1051,0.9932,0.0001</t>
+  </si>
+  <si>
+    <t>0.9366,0.0386,0.0261,0.0049</t>
+  </si>
+  <si>
+    <t>0.0148,0.0159,0.9762,0.0031</t>
+  </si>
+  <si>
+    <t>0.0174,0.1446,0.9495,0.0023</t>
+  </si>
+  <si>
+    <t>0.0533,0.0078,0.9567,0.0020</t>
+  </si>
+  <si>
+    <t>0.0015,0.7435,0.9638,0.0008</t>
+  </si>
+  <si>
+    <t>0.0032,0.0558,0.9912,0.0002</t>
+  </si>
+  <si>
+    <t>0.0096,0.0034,0.9890,0.0010</t>
+  </si>
+  <si>
+    <t>0.0226,0.0067,0.9772,0.0006</t>
+  </si>
+  <si>
+    <t>0.1273,0.0288,0.8737,0.0150</t>
+  </si>
+  <si>
+    <t>0.5958,0.0720,0.3621,0.0033</t>
+  </si>
+  <si>
+    <t>0.2944,0.0265,0.7797,0.0050</t>
+  </si>
+  <si>
+    <t>0.5266,0.1467,0.3570,0.0077</t>
+  </si>
+  <si>
+    <t>0.0346,0.6491,0.6448,0.0053</t>
+  </si>
+  <si>
+    <t>0.4304,0.2859,0.2081,0.0026</t>
+  </si>
+  <si>
+    <t>0.6983,0.0146,0.2601,0.0432</t>
+  </si>
+  <si>
+    <t>0.3254,0.0136,0.7713,0.0069</t>
+  </si>
+  <si>
+    <t>0.8191,0.2977,0.0063,0.0006</t>
+  </si>
+  <si>
+    <t>0.6115,0.5000,0.0046,0.0017</t>
+  </si>
+  <si>
+    <t>0.8991,0.1591,0.0042,0.0025</t>
+  </si>
+  <si>
+    <t>0.9852,0.0158,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.7323,0.3899,0.0069,0.0013</t>
+  </si>
+  <si>
+    <t>0.7044,0.0720,0.2559,0.0069</t>
+  </si>
+  <si>
+    <t>0.7852,0.0189,0.1769,0.0242</t>
+  </si>
+  <si>
+    <t>0.7510,0.0165,0.1654,0.0504</t>
+  </si>
+  <si>
+    <t>0.5439,0.0331,0.4787,0.0315</t>
+  </si>
+  <si>
+    <t>0.7728,0.0187,0.1485,0.0388</t>
+  </si>
+  <si>
+    <t>0.0071,0.0023,0.8949,0.4796</t>
+  </si>
+  <si>
+    <t>0.0498,0.2028,0.8654,0.0025</t>
+  </si>
+  <si>
+    <t>0.0989,0.1020,0.8420,0.0242</t>
+  </si>
+  <si>
+    <t>0.0589,0.1693,0.9143,0.0016</t>
+  </si>
+  <si>
+    <t>0.0156,0.6169,0.7382,0.0076</t>
+  </si>
+  <si>
+    <t>0.9838,0.0081,0.0002,0.0027</t>
+  </si>
+  <si>
+    <t>0.9815,0.0211,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9847,0.0103,0.0015,0.0016</t>
+  </si>
+  <si>
+    <t>0.9930,0.0064,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9775,0.0214,0.0019,0.0013</t>
+  </si>
+  <si>
+    <t>0.9964,0.0018,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9891,0.0056,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.9958,0.0011,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.0222,0.0134,0.9778,0.0014</t>
+  </si>
+  <si>
+    <t>0.1443,0.7262,0.3031,0.0133</t>
+  </si>
+  <si>
+    <t>0.5580,0.0509,0.3076,0.0863</t>
+  </si>
+  <si>
+    <t>0.0130,0.0304,0.9838,0.0006</t>
+  </si>
+  <si>
+    <t>0.0016,0.1084,0.9846,0.0018</t>
+  </si>
+  <si>
+    <t>0.0505,0.0652,0.8835,0.0006</t>
+  </si>
+  <si>
+    <t>0.0022,0.0079,0.9971,0.0001</t>
+  </si>
+  <si>
+    <t>0.0243,0.0299,0.9287,0.0320</t>
+  </si>
+  <si>
+    <t>0.0048,0.0207,0.9889,0.0012</t>
+  </si>
+  <si>
+    <t>0.0081,0.0298,0.9444,0.0338</t>
+  </si>
+  <si>
+    <t>0.2749,0.0508,0.7363,0.0271</t>
+  </si>
+  <si>
+    <t>0.2981,0.0388,0.7400,0.0073</t>
+  </si>
+  <si>
+    <t>0.6716,0.0047,0.4646,0.0033</t>
+  </si>
+  <si>
+    <t>0.8334,0.0124,0.1777,0.0026</t>
+  </si>
+  <si>
+    <t>0.9920,0.0035,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9928,0.0051,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9962,0.0021,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9810,0.0219,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9938,0.0017,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9701,0.0499,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9938,0.0054,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9864,0.0103,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.0398,0.3054,0.6405,0.0011</t>
+  </si>
+  <si>
+    <t>0.0040,0.1918,0.9697,0.0001</t>
+  </si>
+  <si>
+    <t>0.0041,0.0305,0.9807,0.0028</t>
+  </si>
+  <si>
+    <t>0.0411,0.1191,0.8749,0.0009</t>
+  </si>
+  <si>
+    <t>0.0076,0.0253,0.9805,0.0016</t>
+  </si>
+  <si>
+    <t>0.2537,0.0281,0.4685,0.3220</t>
+  </si>
+  <si>
+    <t>0.1005,0.0248,0.9008,0.0054</t>
+  </si>
+  <si>
+    <t>0.0150,0.2236,0.5166,0.4013</t>
+  </si>
+  <si>
+    <t>0.9055,0.0141,0.0103,0.0462</t>
+  </si>
+  <si>
+    <t>0.0153,0.1947,0.0047,0.9734</t>
+  </si>
+  <si>
+    <t>0.0380,0.0005,0.0020,0.9861</t>
+  </si>
+  <si>
+    <t>0.0032,0.0005,0.0112,0.9944</t>
+  </si>
+  <si>
+    <t>0.0049,0.0009,0.0018,0.9966</t>
+  </si>
+  <si>
+    <t>0.6989,0.0118,0.0373,0.2855</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2161,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2413,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2920,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3575,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,10 +4457,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4541,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4611,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4628,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4793,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4863,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4908,7 @@
         <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
